--- a/artfynd/S 1641-2023 artfynd.xlsx
+++ b/artfynd/S 1641-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097747</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1278,6 +1303,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097736</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1400,6 +1430,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097768</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1521,6 +1556,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097702</t>
         </is>
       </c>
     </row>
@@ -1884,6 +1934,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101362325</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101446</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2089,6 +2149,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107070184</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2186,6 +2251,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101341</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2283,6 +2353,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101479</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2391,6 +2466,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107070424</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2512,6 +2592,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097683</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2633,6 +2718,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097721</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2754,6 +2844,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097748</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2853,6 +2948,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67989959</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2974,6 +3074,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097720</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3096,6 +3201,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097744</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3212,6 +3322,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097741</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3320,6 +3435,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107067008</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3428,6 +3548,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107067258</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3530,6 +3655,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116480329</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3641,6 +3771,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113539405</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3738,6 +3873,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101271</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3835,6 +3975,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130101447</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3943,6 +4088,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107066758</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4051,6 +4201,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107069033</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4159,6 +4314,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107070429</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4280,6 +4440,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097775</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4401,6 +4566,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097742</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4522,6 +4692,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097713</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4643,6 +4818,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097739</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4764,6 +4944,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097771</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4872,6 +5057,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107086437</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4980,6 +5170,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107066874</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5081,6 +5276,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99695719</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5189,6 +5389,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107069579</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5297,6 +5502,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107071613</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5405,6 +5615,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107087250</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5526,6 +5741,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097694</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5647,6 +5867,11 @@
           <t>Hur påverkas lavfloran vid frihuggning av ek? Effekter på den totala lavfloran och rödlistade lavar.</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121097693</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5749,6 +5974,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63208315</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5851,6 +6081,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63208316</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5953,6 +6188,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63208317</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6055,6 +6295,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63208318</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6165,6 +6410,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100753329</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6266,6 +6516,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99695721</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6374,8 +6629,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107067273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>